--- a/forms/trg/Formulir_TRG_ait.xlsx
+++ b/forms/trg/Formulir_TRG_ait.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B24)</f>
+        <f>COUNTA(Anggota!B5:B25)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F24)</f>
+        <f>COUNTA(Anggota!F5:F25)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,27 +925,39 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Lecturer 7</t>
+          <t>Associate Professor Ir. Elyas Palantei, M.Eng., Ph.D</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Wireless communication technologies || Antenna Modeling and Fabrication || Optical Fiber Network || Intelligent Antenna and System</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-8876-4926</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6005376</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>24483780700</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -958,12 +970,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Lecturer 5</t>
+          <t>Lecturer 7</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -991,12 +1003,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Eng. Intan Sari Areni., ST., MT.</t>
+          <t>Lecturer 5</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1009,21 +1021,9 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-6248-3656</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>5975448</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>38361089400</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Andini Dani Achmad, S.T., M.T</t>
+          <t>Prof. Dr. Eng. Intan Sari Areni., ST., MT.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1056,17 +1056,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4225-8248</t>
+          <t>0000-0002-6248-3656</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6017516</t>
+          <t>5975448</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57213171565</t>
+          <t>38361089400</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. dr. Rina Masadah, Sp.PA.,M.Phil.DFM</t>
+          <t>Andini Dani Achmad, S.T., M.T</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1099,9 +1099,21 @@
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-4225-8248</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>6017516</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>57213171565</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1114,12 +1126,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Azran Budi Arief, S.T.,M.T</t>
+          <t>Prof. Dr. dr. Rina Masadah, Sp.PA.,M.Phil.DFM</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1132,16 +1144,8 @@
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-2590-719X</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>6736818</t>
-        </is>
-      </c>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
@@ -1155,17 +1159,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Professor Ir. Riza Sulaiman, Ph.D</t>
+          <t>Azran Budi Arief, S.T.,M.T</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Institute for Visual Informatics (IVI), Universiti Kebangsaan Malaysia (UKM), Bangi Campus, Selangor Darul Ehsan, Malaysia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="n"/>
@@ -1173,8 +1177,16 @@
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-2590-719X</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6736818</t>
+        </is>
+      </c>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
@@ -1188,17 +1200,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Associate Professor Dr. Sascha Stegen</t>
+          <t>Professor Ir. Riza Sulaiman, Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Electrical and Electronic Engineering Department, School of Engineering and Built Environment, Griffith University, Nathan Campus, Brisbane, Queenslands, Australia</t>
+          <t>Institute for Visual Informatics (IVI), Universiti Kebangsaan Malaysia (UKM), Bangi Campus, Selangor Darul Ehsan, Malaysia</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -1206,11 +1218,7 @@
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-5654-1215</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
@@ -1223,18 +1231,38 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Associate Professor Dr. Sascha Stegen</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Electrical and Electronic Engineering Department, School of Engineering and Built Environment, Griffith University, Nathan Campus, Brisbane, Queenslands, Australia</t>
+        </is>
+      </c>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-5654-1215</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1423,15 +1451,32 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
